--- a/dat/HGBT.xlsx
+++ b/dat/HGBT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imedk\github\hgbt_app\dat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781E8445-E430-43CB-97D4-A7CB31587C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DFF0E8-8B26-46C2-B41B-ED00B3939AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2512" yWindow="2512" windowWidth="16201" windowHeight="9308" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3188" yWindow="3188" windowWidth="16200" windowHeight="9307" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="46">
   <si>
     <t>Tahun</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>HGBT</t>
   </si>
 </sst>
 </file>
@@ -12004,7 +12007,7 @@
         <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>44</v>
